--- a/qa/excel-reports/Bug List.xlsx
+++ b/qa/excel-reports/Bug List.xlsx
@@ -211,7 +211,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">No fix commit found</t>
+          <t xml:space="preserve">No fix commit recorded</t>
         </is>
       </c>
     </row>
@@ -239,7 +239,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">No fix commit found</t>
+          <t xml:space="preserve">No fix commit recorded</t>
         </is>
       </c>
     </row>
@@ -265,7 +265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -292,7 +292,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-18 by qa/excel-reports/generate_reports.py, against run reg-20261017-01 (2026-10-17).</t>
+          <t xml:space="preserve">2026-10-18 by qa/excel-reports/generate_reports.py after run reg-20261018-01.</t>
         </is>
       </c>
     </row>
@@ -304,55 +304,79 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 bugs: 0 FIXED, 2 NOT FIXED.</t>
+          <t xml:space="preserve">2 bugs: 0 FIXED, 2 NOT FIXED, 0 suspected (confirmation pending).</t>
         </is>
       </c>
     </row>
     <row r="4" ht="42.6" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Source</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">qa/excel-reports/bugs.json is the bug registry: edit descriptions, links, Git references and classifications there (changes made only in this workbook are overwritten, except new bugs and Git references, which are imported).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="42.6" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Automatic bugs</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A failing test that is neither linked to a bug nor listed in not_bugs gets a SUSPECTED bug automatically. Triage it in bugs.json: confirm it, group related tests, or move the test to not_bugs when the test or the environment is at fault.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="29.4" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FIXED only when every linked test is OK in its latest execution. A recorded fix commit without a passing test stays NOT FIXED with "verification pending" in the description.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42.6" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Git Commit / Push</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">From bugs.json: commit hash, branch, and "pushed" only when the remote branch is confirmed to contain the commit. For a fix verified without a recorded commit, the run and commit at which the linked tests passed are shown, with "push not verified".</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16.2" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Date</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The date the bug was first identified; never changed by regeneration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="29.4" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Scope</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Application defects confirmed by a failing test. Failures caused by test code or the environment are explained in Test Results.xlsx instead. Suspected issues without a failing test (SUS-01…08) stay in qa/reports/run-20261016-final/defect-report.md.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="29.4" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Status</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FIXED only when every linked test passes in the latest run. A committed fix without a passing test stays NOT FIXED with "verification pending" in the description.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="42.6" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Git Commit / Push</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Commit hash and branch of the fix, and "pushed" only when the remote branch is confirmed to contain it; otherwise "push not verified". "No fix commit found": git log of the bug's source file shows no change after the bug was found (checked 2026-10-18 at c186696).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16.2" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Date</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The date the bug was first identified; kept when the report is regenerated.</t>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Application defects confirmed or suspected from failing tests. Suspected issues without a failing test (SUS-01…08) stay in qa/reports/run-20261016-final/defect-report.md.</t>
         </is>
       </c>
     </row>
